--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 26,10,26 лгрсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 26,10,26 лгрсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B434AEC0-1803-4174-B770-C41FA5B8D23C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EEB07A-D514-4E22-A1E7-DE1D14408954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,20 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AE$107</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="165">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -542,6 +534,9 @@
   </si>
   <si>
     <t>вместо 7647</t>
+  </si>
+  <si>
+    <t>ротация на код 7520</t>
   </si>
 </sst>
 </file>
@@ -1673,7 +1668,7 @@
         <v>7.0902000000000003</v>
       </c>
       <c r="Q8" s="4">
-        <f t="shared" ref="Q7:Q18" si="7">14*P8-O8-F8</f>
+        <f t="shared" ref="Q8:Q16" si="7">14*P8-O8-F8</f>
         <v>29.7498</v>
       </c>
       <c r="R8" s="5">
@@ -3852,7 +3847,7 @@
         <v>67.140200000000007</v>
       </c>
       <c r="Q28" s="4">
-        <f t="shared" ref="Q20:Q31" si="9">14*P28-O28-F28</f>
+        <f t="shared" ref="Q28:Q30" si="9">14*P28-O28-F28</f>
         <v>320.19080000000014</v>
       </c>
       <c r="R28" s="5">
@@ -4508,7 +4503,7 @@
         <v>21.66</v>
       </c>
       <c r="Q34" s="4">
-        <f t="shared" ref="Q33:Q40" si="11">14*P34-O34-F34</f>
+        <f t="shared" ref="Q34:Q40" si="11">14*P34-O34-F34</f>
         <v>8.298000000000016</v>
       </c>
       <c r="R34" s="5">
@@ -5378,7 +5373,7 @@
         <v>25</v>
       </c>
       <c r="Q42" s="4">
-        <f t="shared" ref="Q42:Q50" si="16">14*P42-O42-F42</f>
+        <f t="shared" ref="Q42:Q49" si="16">14*P42-O42-F42</f>
         <v>104</v>
       </c>
       <c r="R42" s="5">
@@ -5468,7 +5463,7 @@
         <v>45</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5">
@@ -11488,7 +11483,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="Q99" s="4">
-        <f t="shared" ref="Q96:Q99" si="25">14*P99-O99-F99</f>
+        <f t="shared" ref="Q99" si="25">14*P99-O99-F99</f>
         <v>168.80000000000007</v>
       </c>
       <c r="R99" s="5">
@@ -11781,7 +11776,7 @@
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
       <c r="L102" s="5">
-        <f t="shared" ref="L102:L133" si="26">E102-K102</f>
+        <f t="shared" ref="L102:L107" si="26">E102-K102</f>
         <v>0</v>
       </c>
       <c r="M102" s="5"/>
@@ -11795,7 +11790,7 @@
       </c>
       <c r="Q102" s="4"/>
       <c r="R102" s="5" t="e">
-        <f t="shared" ref="R102:R133" si="28">(F102+O102+Q102)/P102</f>
+        <f t="shared" ref="R102:R107" si="28">(F102+O102+Q102)/P102</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S102" s="5" t="e">
@@ -12013,7 +12008,7 @@
         <v>46.6</v>
       </c>
       <c r="Q104" s="4">
-        <f t="shared" ref="Q102:Q107" si="31">14*P104-O104-F104</f>
+        <f t="shared" ref="Q104:Q107" si="31">14*P104-O104-F104</f>
         <v>236.39999999999998</v>
       </c>
       <c r="R104" s="5">
